--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5958,6 +5958,114 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>22 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>22 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>22 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>22 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6066,6 +6066,114 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>23 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>23 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>23 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>23 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -461,11 +461,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>32</t>
@@ -488,11 +484,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>63</t>
@@ -515,11 +507,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>08</t>
@@ -542,11 +530,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>95</t>
@@ -569,11 +553,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>64</t>
@@ -596,11 +576,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>12</t>
@@ -623,11 +599,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>37</t>
@@ -650,11 +622,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>971</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>71</t>
@@ -677,11 +645,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>51</t>
@@ -704,11 +668,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>28</t>
@@ -731,11 +691,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>84</t>
@@ -758,11 +714,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>32</t>
@@ -785,11 +737,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>12</t>
@@ -812,11 +760,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>42</t>
@@ -839,11 +783,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>01</t>
@@ -866,11 +806,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>013</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>13</t>
@@ -893,11 +829,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>41</t>
@@ -920,11 +852,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>01</t>
@@ -947,11 +875,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>21</t>
@@ -974,11 +898,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>69</t>
@@ -1001,11 +921,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>40</t>
@@ -1028,11 +944,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>83</t>
@@ -1055,11 +967,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>27</t>
@@ -1082,11 +990,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>10</t>
@@ -1109,11 +1013,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>47</t>
@@ -1136,11 +1036,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>52</t>
@@ -1163,11 +1059,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>65</t>
@@ -1190,11 +1082,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>14</t>
@@ -1217,11 +1105,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>92</t>
@@ -1244,11 +1128,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>94</t>
@@ -1271,11 +1151,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>54</t>
@@ -1298,11 +1174,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>36</t>
@@ -1325,11 +1197,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>23</t>
@@ -1352,11 +1220,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>054</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>54</t>
@@ -1379,11 +1243,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>74</t>
@@ -1406,11 +1266,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>58</t>
@@ -1433,11 +1289,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>17</t>
@@ -1460,11 +1312,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>73</t>
@@ -1487,11 +1335,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>26</t>
@@ -1514,11 +1358,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>78</t>
@@ -1541,11 +1381,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>33</t>
@@ -1568,11 +1404,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>86</t>
@@ -1595,11 +1427,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>99</t>
@@ -1622,11 +1450,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>68</t>
@@ -1649,11 +1473,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>38</t>
@@ -1676,11 +1496,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>03</t>
@@ -1703,11 +1519,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>037</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>37</t>
@@ -1730,11 +1542,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>92</t>
@@ -1757,11 +1565,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>69</t>
@@ -1784,11 +1588,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>39</t>
@@ -1811,11 +1611,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>61</t>
@@ -1838,11 +1634,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>28</t>
@@ -6171,6 +5963,114 @@
       <c r="E213" t="inlineStr">
         <is>
           <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>24 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>24 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>098</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>24 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>24 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6074,6 +6074,114 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>25 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>25 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>25 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>25 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6182,6 +6182,114 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>090</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6290,6 +6290,114 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>27 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>27 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>27 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>27 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6382,11 +6382,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>11</t>
@@ -6395,6 +6391,114 @@
       <c r="E229" t="inlineStr">
         <is>
           <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>28 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>28 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>28 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>28 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6502,6 +6502,114 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>29 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>29 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>29 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>29 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6610,6 +6610,114 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>30 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>30 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>30 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>30 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6718,6 +6718,114 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6826,6 +6826,114 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6934,6 +6934,114 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>3 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>3 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>3 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>3 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7042,6 +7042,114 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>4 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>4 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>4 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>4 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7150,6 +7150,60 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>5 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>5 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7161,11 +7161,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>17</t>
@@ -7188,11 +7184,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
+      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>30</t>
@@ -7201,6 +7193,114 @@
       <c r="E259" t="inlineStr">
         <is>
           <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E263"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7158,18 +7158,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>ฮานอยพิเศษ</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -7181,72 +7185,76 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ฮานอยเฉพาะกิจ</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>5 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ฮานอย</t>
+          <t>ฮานอยพิเศษ</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>017</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>5 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ฮานอย VIP</t>
+          <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>630</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -7258,22 +7266,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ฮานอยพิเศษ</t>
+          <t>ฮานอย</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>497</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>03</t>
         </is>
       </c>
     </row>
@@ -7285,22 +7293,184 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E265" t="inlineStr">
         <is>
           <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>7 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>7 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>7 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>7 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E269"/>
+  <dimension ref="A1:E273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7474,6 +7474,114 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>8 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>089</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>8 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>8 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>8 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7582,6 +7582,114 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>9 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>9 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>9 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>9 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1657,11 +1657,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>94</t>
@@ -1684,11 +1680,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>032</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>32</t>
@@ -1711,11 +1703,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>81</t>
@@ -1738,11 +1726,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>50</t>
@@ -1765,11 +1749,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>04</t>
@@ -1792,11 +1772,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>72</t>
@@ -1819,11 +1795,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>96</t>
@@ -1846,11 +1818,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>27</t>
@@ -1873,11 +1841,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>84</t>
@@ -1900,11 +1864,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>81</t>
@@ -1927,11 +1887,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>030</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>30</t>
@@ -1954,11 +1910,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>06</t>
@@ -1981,11 +1933,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>61</t>
@@ -2008,11 +1956,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>67</t>
@@ -2035,11 +1979,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>21</t>
@@ -2062,11 +2002,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>843</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>43</t>
@@ -2089,11 +2025,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>54</t>
@@ -2116,11 +2048,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>61</t>
@@ -2143,11 +2071,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>98</t>
@@ -2170,11 +2094,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>42</t>
@@ -2197,11 +2117,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>68</t>
@@ -2224,11 +2140,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>053</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>53</t>
@@ -2251,11 +2163,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>92</t>
@@ -2278,11 +2186,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>55</t>
@@ -7687,6 +7591,114 @@
       <c r="E277" t="inlineStr">
         <is>
           <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>10 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>10 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>10 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>10 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7702,6 +7702,114 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>11 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>11 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>11 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>082</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>11 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>061</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7810,6 +7810,87 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>12 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>12 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>12 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>045</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7891,6 +7891,114 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>13 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>13 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>13 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>13 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7999,6 +7999,114 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>14 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>14 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>14 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>14 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E296"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8107,6 +8107,114 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>15 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>15 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>15 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>15 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8215,6 +8215,114 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>16 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>16 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>16 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>16 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8323,6 +8323,114 @@
         </is>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>17 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>17 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>17 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>17 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8431,6 +8431,114 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>18 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>18 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>18 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>18 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E312"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8539,6 +8539,114 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>19 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>19 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>19 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>19 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8647,6 +8647,114 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E320"/>
+  <dimension ref="A1:E324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8755,6 +8755,114 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>21 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>21 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>21 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>21 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E324"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2209,11 +2209,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>85</t>
@@ -2236,11 +2232,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>18</t>
@@ -2263,11 +2255,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>24</t>
@@ -2290,11 +2278,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>74</t>
@@ -2317,11 +2301,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>39</t>
@@ -2344,11 +2324,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>27</t>
@@ -2371,11 +2347,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>33</t>
@@ -2398,11 +2370,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>90</t>
@@ -2425,11 +2393,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>21</t>
@@ -2452,11 +2416,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>81</t>
@@ -2479,11 +2439,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>66</t>
@@ -2506,11 +2462,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>45</t>
@@ -2533,11 +2485,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>04</t>
@@ -2560,11 +2508,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>50</t>
@@ -2587,11 +2531,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>26</t>
@@ -2614,11 +2554,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>56</t>
@@ -2641,11 +2577,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>81</t>
@@ -2668,11 +2600,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>53</t>
@@ -2695,11 +2623,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>08</t>
@@ -2722,11 +2646,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>21</t>
@@ -2749,11 +2669,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>11</t>
@@ -2776,11 +2692,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>85</t>
@@ -2803,11 +2715,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>00</t>
@@ -2830,11 +2738,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>96</t>
@@ -8860,6 +8764,114 @@
       <c r="E324" t="inlineStr">
         <is>
           <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>22 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>22 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>22 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>22 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>57</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8875,6 +8875,114 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>23 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>23 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>23 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>23 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E332"/>
+  <dimension ref="A1:E336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2761,11 +2761,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>13</t>
@@ -2788,11 +2784,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>32</t>
@@ -2815,11 +2807,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>26</t>
@@ -2842,11 +2830,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>023</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>23</t>
@@ -2869,11 +2853,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>50</t>
@@ -2896,11 +2876,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>16</t>
@@ -2923,11 +2899,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>86</t>
@@ -2950,11 +2922,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>48</t>
@@ -2977,11 +2945,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>54</t>
@@ -3004,11 +2968,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>030</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>30</t>
@@ -3031,11 +2991,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>064</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>64</t>
@@ -3058,11 +3014,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>089</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>89</t>
@@ -3085,11 +3037,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>43</t>
@@ -3112,11 +3060,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>31</t>
@@ -3139,11 +3083,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>55</t>
@@ -3166,11 +3106,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>73</t>
@@ -3193,11 +3129,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>042</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>42</t>
@@ -3220,11 +3152,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>38</t>
@@ -3247,11 +3175,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>20</t>
@@ -3274,11 +3198,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>97</t>
@@ -3301,11 +3221,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>53</t>
@@ -3328,11 +3244,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>91</t>
@@ -3355,11 +3267,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>81</t>
@@ -3382,11 +3290,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>63</t>
@@ -3409,11 +3313,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>23</t>
@@ -3436,11 +3336,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>16</t>
@@ -3463,11 +3359,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>64</t>
@@ -3490,11 +3382,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>40</t>
@@ -3517,11 +3405,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>36</t>
@@ -3544,11 +3428,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>93</t>
@@ -3571,11 +3451,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>091</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>91</t>
@@ -3598,11 +3474,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>075</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>75</t>
@@ -3625,11 +3497,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>83</t>
@@ -3652,11 +3520,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>18</t>
@@ -3679,11 +3543,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>093</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>93</t>
@@ -3706,11 +3566,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>61</t>
@@ -3733,11 +3589,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>78</t>
@@ -3760,11 +3612,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>21</t>
@@ -3787,11 +3635,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
-      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>80</t>
@@ -3814,11 +3658,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>29</t>
@@ -3841,11 +3681,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>65</t>
@@ -3868,11 +3704,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>93</t>
@@ -3895,11 +3727,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>99</t>
@@ -3922,11 +3750,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>01</t>
@@ -3949,11 +3773,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>93</t>
@@ -3976,11 +3796,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>55</t>
@@ -4003,11 +3819,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>12</t>
@@ -4030,11 +3842,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>28</t>
@@ -4057,11 +3865,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>05</t>
@@ -4084,11 +3888,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>61</t>
@@ -4111,11 +3911,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>05</t>
@@ -4138,11 +3934,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>64</t>
@@ -4165,11 +3957,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>51</t>
@@ -4192,11 +3980,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>49</t>
@@ -4219,11 +4003,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>97</t>
@@ -4246,11 +4026,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>47</t>
@@ -4273,11 +4049,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>08</t>
@@ -4300,11 +4072,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>16</t>
@@ -4327,11 +4095,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>62</t>
@@ -4354,11 +4118,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>19</t>
@@ -8980,6 +8740,114 @@
       <c r="E332" t="inlineStr">
         <is>
           <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>24 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>24 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>24 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>24 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E336"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8851,6 +8851,114 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>25 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>25 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>25 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>25 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8959,6 +8959,114 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>26 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>26 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>26 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>26 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9067,6 +9067,114 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>27 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>27 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>27 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>27 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9175,6 +9175,114 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>28 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>28 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>28 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>28 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E352"/>
+  <dimension ref="A1:E356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9283,6 +9283,114 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>29 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>29 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>29 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>29 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9391,6 +9391,114 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>30 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>30 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>30 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>30 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9499,6 +9499,114 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>31 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>31 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>31 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>31 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E364"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9607,6 +9607,114 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>077</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9715,6 +9715,114 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E372"/>
+  <dimension ref="A1:E376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9823,6 +9823,114 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>3 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>3 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>3 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>3 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E376"/>
+  <dimension ref="A1:E380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9931,6 +9931,114 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>4 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>4 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>4 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>4 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E380"/>
+  <dimension ref="A1:E384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10039,6 +10039,114 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>5 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>5 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>5 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>5 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E384"/>
+  <dimension ref="A1:E392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10147,6 +10147,222 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>6 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>6 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>6 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>6 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>7 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>7 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>7 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>7 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E392"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10363,6 +10363,114 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>8 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>8 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>8 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>8 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10471,6 +10471,114 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>9 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>9 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>9 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>9 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4141,11 +4141,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>83</t>
@@ -4168,11 +4164,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>58</t>
@@ -4195,11 +4187,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>024</t>
-        </is>
-      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>24</t>
@@ -4222,11 +4210,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>72</t>
@@ -4249,11 +4233,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>89</t>
@@ -4276,11 +4256,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>94</t>
@@ -4303,11 +4279,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>61</t>
@@ -4330,11 +4302,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>52</t>
@@ -4357,11 +4325,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>014</t>
-        </is>
-      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>14</t>
@@ -4384,11 +4348,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>97</t>
@@ -4411,11 +4371,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>93</t>
@@ -4438,11 +4394,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>06</t>
@@ -4465,11 +4417,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>00</t>
@@ -4492,11 +4440,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>64</t>
@@ -4519,11 +4463,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>43</t>
@@ -4546,11 +4486,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>07</t>
@@ -4573,11 +4509,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>80</t>
@@ -4600,11 +4532,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>02</t>
@@ -4627,11 +4555,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>096</t>
-        </is>
-      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>96</t>
@@ -4654,11 +4578,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>41</t>
@@ -4681,11 +4601,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>84</t>
@@ -4708,11 +4624,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>90</t>
@@ -4735,11 +4647,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>921</t>
-        </is>
-      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>21</t>
@@ -4762,11 +4670,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>67</t>
@@ -4789,11 +4693,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>03</t>
@@ -4816,11 +4716,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>67</t>
@@ -4843,11 +4739,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>057</t>
-        </is>
-      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>57</t>
@@ -4870,11 +4762,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>35</t>
@@ -4897,11 +4785,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>032</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>32</t>
@@ -4924,11 +4808,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>40</t>
@@ -4951,11 +4831,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>46</t>
@@ -4978,11 +4854,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>26</t>
@@ -5005,11 +4877,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>55</t>
@@ -5032,11 +4900,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>08</t>
@@ -5059,11 +4923,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>982</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>82</t>
@@ -5086,11 +4946,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>20</t>
@@ -5113,11 +4969,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>60</t>
@@ -5140,11 +4992,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>20</t>
@@ -5167,11 +5015,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>59</t>
@@ -5194,11 +5038,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>88</t>
@@ -10576,6 +10416,114 @@
       <c r="E400" t="inlineStr">
         <is>
           <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>10 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>10 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>10 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>092</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>10 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E404"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10527,6 +10527,114 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>11 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>11 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>11 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>11 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10635,6 +10635,114 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>12 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>12 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>12 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>12 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E412"/>
+  <dimension ref="A1:E416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10743,6 +10743,114 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>13 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>13 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>13 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>13 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E416"/>
+  <dimension ref="A1:E420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10851,6 +10851,114 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>14 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>14 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>14 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>14 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E420"/>
+  <dimension ref="A1:E424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10959,6 +10959,114 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>15 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>15 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>15 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>15 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E424"/>
+  <dimension ref="A1:E428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11067,6 +11067,114 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>16 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>16 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>062</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>16 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>16 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E428"/>
+  <dimension ref="A1:E432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11175,6 +11175,114 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>17 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>17 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>17 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>17 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E432"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11283,6 +11283,114 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>18 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>18 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>18 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>18 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E436"/>
+  <dimension ref="A1:E440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11391,6 +11391,114 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>19 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>19 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>19 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>19 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E440"/>
+  <dimension ref="A1:E444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11499,6 +11499,114 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>20 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>20 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>20 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>20 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E444"/>
+  <dimension ref="A1:E460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5061,11 +5061,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>083</t>
-        </is>
-      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>83</t>
@@ -5088,11 +5084,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>02</t>
@@ -5115,11 +5107,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>27</t>
@@ -5142,11 +5130,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>71</t>
@@ -5169,11 +5153,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>36</t>
@@ -5196,11 +5176,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>076</t>
-        </is>
-      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>76</t>
@@ -5223,11 +5199,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>63</t>
@@ -5250,11 +5222,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>04</t>
@@ -5277,11 +5245,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>37</t>
@@ -5304,11 +5268,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>42</t>
@@ -5331,11 +5291,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>31</t>
@@ -5358,11 +5314,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>56</t>
@@ -5385,11 +5337,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>51</t>
@@ -5412,11 +5360,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>098</t>
-        </is>
-      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>98</t>
@@ -5439,11 +5383,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>66</t>
@@ -5466,11 +5406,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>034</t>
-        </is>
-      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>34</t>
@@ -5493,11 +5429,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>16</t>
@@ -5520,11 +5452,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>31</t>
@@ -5547,11 +5475,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>61</t>
@@ -5574,11 +5498,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>81</t>
@@ -5601,11 +5521,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
+      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>04</t>
@@ -5628,11 +5544,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>090</t>
-        </is>
-      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>90</t>
@@ -5655,11 +5567,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
+      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>13</t>
@@ -5682,11 +5590,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
+      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>63</t>
@@ -5709,11 +5613,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>53</t>
@@ -5736,11 +5636,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>040</t>
-        </is>
-      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>40</t>
@@ -5763,11 +5659,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>859</t>
-        </is>
-      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>59</t>
@@ -5813,11 +5705,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
+      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>52</t>
@@ -5840,11 +5728,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>38</t>
@@ -5867,11 +5751,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
+      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>23</t>
@@ -5894,11 +5774,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>12</t>
@@ -5921,11 +5797,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
+      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>42</t>
@@ -5948,11 +5820,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>031</t>
-        </is>
-      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>31</t>
@@ -5975,11 +5843,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>27</t>
@@ -6002,11 +5866,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>08</t>
@@ -6029,11 +5889,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>68</t>
@@ -6056,11 +5912,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>79</t>
@@ -6083,11 +5935,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>28</t>
@@ -6110,11 +5958,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>97</t>
@@ -6137,11 +5981,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>54</t>
@@ -6164,11 +6004,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>10</t>
@@ -6191,11 +6027,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
+      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>32</t>
@@ -6218,11 +6050,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>58</t>
@@ -6245,11 +6073,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>39</t>
@@ -6272,11 +6096,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
+      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>61</t>
@@ -6299,11 +6119,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
+      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>13</t>
@@ -6326,11 +6142,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>39</t>
@@ -6353,11 +6165,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>65</t>
@@ -6380,11 +6188,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
+      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>86</t>
@@ -6407,11 +6211,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>29</t>
@@ -6434,11 +6234,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>15</t>
@@ -6461,11 +6257,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>87</t>
@@ -6488,11 +6280,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
+      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>56</t>
@@ -6515,11 +6303,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>10</t>
@@ -6542,11 +6326,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
+      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>94</t>
@@ -6569,11 +6349,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>71</t>
@@ -6596,11 +6372,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
+      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>28</t>
@@ -6623,11 +6395,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>17</t>
@@ -6650,11 +6418,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>30</t>
@@ -6677,11 +6441,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>97</t>
@@ -6704,11 +6464,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
+      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>15</t>
@@ -6731,11 +6487,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>64</t>
@@ -6758,11 +6510,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>23</t>
@@ -6785,11 +6533,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>79</t>
@@ -6812,11 +6556,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>064</t>
-        </is>
-      </c>
+      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>64</t>
@@ -6839,11 +6579,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>61</t>
@@ -6866,11 +6602,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>31</t>
@@ -6893,11 +6625,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>089</t>
-        </is>
-      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>89</t>
@@ -6920,11 +6648,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
+      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>13</t>
@@ -6947,11 +6671,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>53</t>
@@ -6974,11 +6694,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
+      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>87</t>
@@ -7001,11 +6717,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>85</t>
@@ -7028,11 +6740,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
+      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>76</t>
@@ -7055,11 +6763,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
+      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>81</t>
@@ -7082,11 +6786,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>29</t>
@@ -7109,11 +6809,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>67</t>
@@ -7136,11 +6832,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>33</t>
@@ -7163,11 +6855,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>42</t>
@@ -7190,11 +6878,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>09</t>
@@ -7217,11 +6901,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>01</t>
@@ -7244,11 +6924,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>46</t>
@@ -7271,11 +6947,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>082</t>
-        </is>
-      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>82</t>
@@ -7298,11 +6970,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>061</t>
-        </is>
-      </c>
+      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>61</t>
@@ -7325,11 +6993,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>94</t>
@@ -7352,11 +7016,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
+      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>75</t>
@@ -7379,11 +7039,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>045</t>
-        </is>
-      </c>
+      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>45</t>
@@ -7406,11 +7062,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
+      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>99</t>
@@ -7433,11 +7085,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>041</t>
-        </is>
-      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>41</t>
@@ -7460,11 +7108,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>57</t>
@@ -7487,11 +7131,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>62</t>
@@ -7514,11 +7154,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>47</t>
@@ -7541,11 +7177,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>92</t>
@@ -7568,11 +7200,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
+      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>94</t>
@@ -7595,11 +7223,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
+      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>40</t>
@@ -7622,11 +7246,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>19</t>
@@ -7649,11 +7269,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>057</t>
-        </is>
-      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>57</t>
@@ -7676,11 +7292,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>08</t>
@@ -7703,11 +7315,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>95</t>
@@ -7730,11 +7338,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>63</t>
@@ -7757,11 +7361,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>32</t>
@@ -7784,11 +7384,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>035</t>
-        </is>
-      </c>
+      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>35</t>
@@ -7811,11 +7407,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
+      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>06</t>
@@ -7838,11 +7430,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>39</t>
@@ -7865,11 +7453,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>048</t>
-        </is>
-      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>48</t>
@@ -7892,11 +7476,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
+      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>25</t>
@@ -7919,11 +7499,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
+      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>22</t>
@@ -7946,11 +7522,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
+      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>90</t>
@@ -7973,11 +7545,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
+      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>35</t>
@@ -8000,11 +7568,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>50</t>
@@ -8027,11 +7591,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>068</t>
-        </is>
-      </c>
+      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>68</t>
@@ -8054,11 +7614,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
+      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>38</t>
@@ -8081,11 +7637,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>043</t>
-        </is>
-      </c>
+      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>43</t>
@@ -8108,11 +7660,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>055</t>
-        </is>
-      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>55</t>
@@ -8135,11 +7683,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>37</t>
@@ -8162,11 +7706,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>28</t>
@@ -8189,11 +7729,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>38</t>
@@ -8216,11 +7752,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
+      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>86</t>
@@ -8243,11 +7775,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
+      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>24</t>
@@ -8270,11 +7798,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>070</t>
-        </is>
-      </c>
+      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>70</t>
@@ -8297,11 +7821,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>10</t>
@@ -8324,11 +7844,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
+      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>84</t>
@@ -8351,11 +7867,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>55</t>
@@ -8378,11 +7890,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>54</t>
@@ -8405,11 +7913,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>31</t>
@@ -8432,11 +7936,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>53</t>
@@ -8459,11 +7959,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>13</t>
@@ -8486,11 +7982,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>54</t>
@@ -8513,11 +8005,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>49</t>
@@ -8540,11 +8028,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>76</t>
@@ -8567,11 +8051,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>98</t>
@@ -8594,11 +8074,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>38</t>
@@ -8621,11 +8097,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>01</t>
@@ -8648,11 +8120,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>06</t>
@@ -8675,11 +8143,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>74</t>
@@ -8702,11 +8166,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>28</t>
@@ -8729,11 +8189,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
+      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>65</t>
@@ -8756,11 +8212,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
+      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>53</t>
@@ -8783,11 +8235,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>50</t>
@@ -8810,11 +8258,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
+      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>16</t>
@@ -8837,11 +8281,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
+      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>02</t>
@@ -8864,11 +8304,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
+      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>32</t>
@@ -8891,11 +8327,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>057</t>
-        </is>
-      </c>
+      <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
           <t>57</t>
@@ -8918,11 +8350,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
+      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>96</t>
@@ -8945,11 +8373,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
+      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>11</t>
@@ -8972,11 +8396,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>035</t>
-        </is>
-      </c>
+      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>35</t>
@@ -8999,11 +8419,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>84</t>
@@ -9026,11 +8442,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>00</t>
@@ -9053,11 +8465,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>06</t>
@@ -9080,11 +8488,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>76</t>
@@ -9107,11 +8511,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>54</t>
@@ -9134,11 +8534,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
+      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>83</t>
@@ -9161,11 +8557,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>87</t>
@@ -9188,11 +8580,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>72</t>
@@ -9215,11 +8603,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>32</t>
@@ -9242,11 +8626,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>34</t>
@@ -9269,11 +8649,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>75</t>
@@ -9296,11 +8672,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>065</t>
-        </is>
-      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>65</t>
@@ -9323,11 +8695,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>10</t>
@@ -9350,11 +8718,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>10</t>
@@ -9377,11 +8741,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>05</t>
@@ -9404,11 +8764,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>33</t>
@@ -9431,11 +8787,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
+      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>18</t>
@@ -9458,11 +8810,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>23</t>
@@ -9485,11 +8833,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
+      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>36</t>
@@ -9512,11 +8856,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>43</t>
@@ -9539,11 +8879,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>077</t>
-        </is>
-      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>77</t>
@@ -9566,11 +8902,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
+      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
           <t>09</t>
@@ -9593,11 +8925,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>31</t>
@@ -9620,11 +8948,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
           <t>03</t>
@@ -9647,11 +8971,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
           <t>46</t>
@@ -9674,11 +8994,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
+      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>47</t>
@@ -9701,11 +9017,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>64</t>
@@ -9728,11 +9040,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>71</t>
@@ -9755,11 +9063,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>39</t>
@@ -9782,11 +9086,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
+      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>25</t>
@@ -9809,11 +9109,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
+      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>41</t>
@@ -9836,11 +9132,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>81</t>
@@ -9863,11 +9155,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>91</t>
@@ -9890,11 +9178,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>60</t>
@@ -9917,11 +9201,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>95</t>
@@ -9944,11 +9224,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>64</t>
@@ -9971,11 +9247,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>34</t>
@@ -9998,11 +9270,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>67</t>
@@ -10025,11 +9293,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
+      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>73</t>
@@ -10052,11 +9316,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
+      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>63</t>
@@ -10079,11 +9339,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
+      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
           <t>07</t>
@@ -10106,11 +9362,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
+      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
           <t>79</t>
@@ -10133,11 +9385,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
+      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
           <t>29</t>
@@ -10160,11 +9408,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>023</t>
-        </is>
-      </c>
+      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>23</t>
@@ -10187,11 +9431,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
+      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
           <t>65</t>
@@ -10214,11 +9454,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
+      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>22</t>
@@ -10241,11 +9477,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
+      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
           <t>94</t>
@@ -10268,11 +9500,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>060</t>
-        </is>
-      </c>
+      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
           <t>60</t>
@@ -10295,11 +9523,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
+      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
           <t>28</t>
@@ -10322,11 +9546,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
+      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>21</t>
@@ -10349,11 +9569,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
+      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>47</t>
@@ -10376,11 +9592,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
+      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
           <t>91</t>
@@ -10403,11 +9615,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
+      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>50</t>
@@ -10430,11 +9638,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
+      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>57</t>
@@ -10457,11 +9661,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
+      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>85</t>
@@ -10484,11 +9684,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>092</t>
-        </is>
-      </c>
+      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
           <t>92</t>
@@ -10511,11 +9707,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
+      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>92</t>
@@ -10538,11 +9730,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
+      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
           <t>91</t>
@@ -10565,11 +9753,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
+      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
           <t>24</t>
@@ -10592,11 +9776,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
+      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
           <t>87</t>
@@ -10619,11 +9799,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
+      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>16</t>
@@ -10646,11 +9822,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
+      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>26</t>
@@ -10673,11 +9845,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
+      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
           <t>25</t>
@@ -10700,11 +9868,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
+      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
           <t>86</t>
@@ -10727,11 +9891,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
+      <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
           <t>74</t>
@@ -10754,11 +9914,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
+      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
           <t>44</t>
@@ -10781,11 +9937,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
+      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>82</t>
@@ -10808,11 +9960,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>051</t>
-        </is>
-      </c>
+      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>51</t>
@@ -10835,11 +9983,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
+      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>09</t>
@@ -10862,11 +10006,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>018</t>
-        </is>
-      </c>
+      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>18</t>
@@ -10889,11 +10029,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
+      <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
           <t>21</t>
@@ -10916,11 +10052,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>013</t>
-        </is>
-      </c>
+      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
           <t>13</t>
@@ -10943,11 +10075,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
+      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
           <t>81</t>
@@ -10970,11 +10098,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
+      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
           <t>78</t>
@@ -10997,11 +10121,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
+      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
           <t>81</t>
@@ -11024,11 +10144,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
+      <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
           <t>05</t>
@@ -11051,11 +10167,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
+      <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
           <t>85</t>
@@ -11078,11 +10190,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
+      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
           <t>96</t>
@@ -11105,11 +10213,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>062</t>
-        </is>
-      </c>
+      <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
           <t>62</t>
@@ -11132,11 +10236,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
+      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
           <t>70</t>
@@ -11159,11 +10259,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
+      <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
           <t>05</t>
@@ -11186,11 +10282,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
+      <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
           <t>39</t>
@@ -11213,11 +10305,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
+      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>97</t>
@@ -11240,11 +10328,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
+      <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
           <t>72</t>
@@ -11267,11 +10351,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
+      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
           <t>95</t>
@@ -11294,11 +10374,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
+      <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
           <t>83</t>
@@ -11321,11 +10397,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
+      <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
           <t>44</t>
@@ -11348,11 +10420,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
+      <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
           <t>58</t>
@@ -11375,11 +10443,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
+      <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
           <t>40</t>
@@ -11402,11 +10466,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
+      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
           <t>43</t>
@@ -11429,11 +10489,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
-      </c>
+      <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
           <t>62</t>
@@ -11456,11 +10512,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
+      <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
           <t>63</t>
@@ -11483,11 +10535,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
+      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>33</t>
@@ -11510,11 +10558,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
+      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>23</t>
@@ -11537,11 +10581,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
+      <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
           <t>34</t>
@@ -11564,11 +10604,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
+      <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
           <t>77</t>
@@ -11591,11 +10627,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
+      <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
           <t>27</t>
@@ -11604,6 +10636,438 @@
       <c r="E444" t="inlineStr">
         <is>
           <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>22 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>22 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>22 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>22 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>23 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>23 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>23 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>23 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>083</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>24 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>24 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>24 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>24 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>25 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>25 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>25 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>25 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>79</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E460"/>
+  <dimension ref="A1:E463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10650,11 +10650,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
+      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>54</t>
@@ -10677,11 +10673,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+      <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
           <t>31</t>
@@ -10704,11 +10696,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
+      <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
           <t>53</t>
@@ -10731,11 +10719,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
+      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
           <t>13</t>
@@ -11068,6 +11052,87 @@
       <c r="E460" t="inlineStr">
         <is>
           <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>26 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>26 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>26 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E463"/>
+  <dimension ref="A1:E468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11090,22 +11090,22 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>ฮานอยพิเศษ</t>
+          <t>ฮานอย VIP</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>815</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -11117,22 +11117,157 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>ฮานอยเฉพาะกิจ</t>
+          <t>ฮานอยพิเศษ</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>26 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
           <t>663</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr">
+      <c r="D464" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E463" t="inlineStr">
+      <c r="E464" t="inlineStr">
         <is>
           <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>27 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>27 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>093</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>27 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>27 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>62</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E468"/>
+  <dimension ref="A1:E472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10742,11 +10742,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
+      <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
           <t>38</t>
@@ -10769,11 +10765,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+      <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
           <t>41</t>
@@ -10796,11 +10788,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
+      <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
           <t>85</t>
@@ -10823,11 +10811,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>083</t>
-        </is>
-      </c>
+      <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
           <t>83</t>
@@ -10850,11 +10834,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
+      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>17</t>
@@ -10877,11 +10857,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
+      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
           <t>55</t>
@@ -10904,11 +10880,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
+      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
           <t>45</t>
@@ -10931,11 +10903,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
+      <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
           <t>69</t>
@@ -11268,6 +11236,114 @@
       <c r="E468" t="inlineStr">
         <is>
           <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>28 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>28 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>28 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>28 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>53</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E472"/>
+  <dimension ref="A1:E480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10926,11 +10926,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>080</t>
-        </is>
-      </c>
+      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>80</t>
@@ -10953,11 +10949,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
+      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>68</t>
@@ -10980,11 +10972,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
+      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
           <t>11</t>
@@ -11007,11 +10995,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
+      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
           <t>31</t>
@@ -11034,11 +11018,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
+      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>61</t>
@@ -11061,11 +11041,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
+      <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
           <t>15</t>
@@ -11088,11 +11064,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
+      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
           <t>27</t>
@@ -11115,11 +11087,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
+      <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
           <t>63</t>
@@ -11344,6 +11312,222 @@
       <c r="E472" t="inlineStr">
         <is>
           <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>29 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>29 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>082</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>29 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>29 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>30 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>30 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>30 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>30 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E480"/>
+  <dimension ref="A1:E484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11110,11 +11110,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
+      <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
           <t>45</t>
@@ -11137,11 +11133,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>093</t>
-        </is>
-      </c>
+      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
           <t>93</t>
@@ -11164,11 +11156,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
+      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
           <t>34</t>
@@ -11191,11 +11179,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
+      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>78</t>
@@ -11528,6 +11512,114 @@
       <c r="E480" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>31 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>31 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>31 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>31 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>68</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E484"/>
+  <dimension ref="A1:E488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11202,11 +11202,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
+      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>68</t>
@@ -11229,11 +11225,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
+      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>36</t>
@@ -11256,11 +11248,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>51</t>
@@ -11283,11 +11271,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>06</t>
@@ -11620,6 +11604,114 @@
       <c r="E484" t="inlineStr">
         <is>
           <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>1 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>1 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>1 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E488"/>
+  <dimension ref="A1:E492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11294,11 +11294,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
+      <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
           <t>37</t>
@@ -11321,11 +11317,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>082</t>
-        </is>
-      </c>
+      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>82</t>
@@ -11348,11 +11340,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
+      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>54</t>
@@ -11375,11 +11363,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
+      <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
           <t>21</t>
@@ -11712,6 +11696,114 @@
       <c r="E488" t="inlineStr">
         <is>
           <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E492"/>
+  <dimension ref="A1:E496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11386,11 +11386,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
+      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
           <t>72</t>
@@ -11413,11 +11409,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
+      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
           <t>59</t>
@@ -11440,11 +11432,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
           <t>51</t>
@@ -11467,11 +11455,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>054</t>
-        </is>
-      </c>
+      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
           <t>54</t>
@@ -11804,6 +11788,114 @@
       <c r="E492" t="inlineStr">
         <is>
           <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>3 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>3 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>3 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>3 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E496"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11478,11 +11478,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
           <t>44</t>
@@ -11505,11 +11501,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
           <t>38</t>
@@ -11532,11 +11524,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
+      <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
           <t>19</t>
@@ -11559,11 +11547,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
+      <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
           <t>09</t>
@@ -11896,6 +11880,114 @@
       <c r="E496" t="inlineStr">
         <is>
           <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>4 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>4 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>4 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>4 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:E504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11570,11 +11570,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
+      <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
           <t>21</t>
@@ -11597,11 +11593,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
+      <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
           <t>63</t>
@@ -11624,11 +11616,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
+      <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr">
         <is>
           <t>89</t>
@@ -11651,11 +11639,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
+      <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
           <t>31</t>
@@ -11988,6 +11972,114 @@
       <c r="E500" t="inlineStr">
         <is>
           <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>5 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>5 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>5 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>5 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:E508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11662,11 +11662,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
           <t>42</t>
@@ -11689,11 +11685,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr">
         <is>
           <t>91</t>
@@ -11716,11 +11708,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
           <t>61</t>
@@ -11743,11 +11731,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
           <t>48</t>
@@ -12080,6 +12064,114 @@
       <c r="E504" t="inlineStr">
         <is>
           <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>6 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>6 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>6 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>6 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E508"/>
+  <dimension ref="A1:E512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11754,11 +11754,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
           <t>11</t>
@@ -11781,11 +11777,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
           <t>44</t>
@@ -11808,11 +11800,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
           <t>02</t>
@@ -11835,11 +11823,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
+      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr">
         <is>
           <t>08</t>
@@ -12172,6 +12156,114 @@
       <c r="E508" t="inlineStr">
         <is>
           <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>7 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>7 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>7 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>7 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>91</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E512"/>
+  <dimension ref="A1:E516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11846,11 +11846,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>066</t>
-        </is>
-      </c>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
         <is>
           <t>66</t>
@@ -11873,11 +11869,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
           <t>09</t>
@@ -11900,11 +11892,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
+      <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
           <t>03</t>
@@ -11927,11 +11915,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
+      <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
           <t>56</t>
@@ -12264,6 +12248,114 @@
       <c r="E512" t="inlineStr">
         <is>
           <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>8 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>8 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>073</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>8 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>8 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E516"/>
+  <dimension ref="A1:E520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11938,11 +11938,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>037</t>
-        </is>
-      </c>
+      <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
           <t>37</t>
@@ -11965,11 +11961,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>024</t>
-        </is>
-      </c>
+      <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
           <t>24</t>
@@ -11992,11 +11984,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
+      <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
           <t>76</t>
@@ -12019,11 +12007,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>014</t>
-        </is>
-      </c>
+      <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
           <t>14</t>
@@ -12356,6 +12340,114 @@
       <c r="E516" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>9 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>9 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>9 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>9 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>89</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E520"/>
+  <dimension ref="A1:E524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12030,11 +12030,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
+      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
           <t>35</t>
@@ -12057,11 +12053,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
+      <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
           <t>07</t>
@@ -12084,11 +12076,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
+      <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
           <t>05</t>
@@ -12111,11 +12099,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
+      <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr">
         <is>
           <t>97</t>
@@ -12448,6 +12432,114 @@
       <c r="E520" t="inlineStr">
         <is>
           <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>10 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>10 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>10 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>10 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>86</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E524"/>
+  <dimension ref="A1:E528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12122,11 +12122,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
+      <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
         <is>
           <t>90</t>
@@ -12149,11 +12145,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
+      <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
           <t>45</t>
@@ -12176,11 +12168,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
+      <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr">
         <is>
           <t>03</t>
@@ -12203,11 +12191,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
+      <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
         <is>
           <t>46</t>
@@ -12540,6 +12524,114 @@
       <c r="E524" t="inlineStr">
         <is>
           <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>11 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>11 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>11 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>11 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
     </row>

--- a/hanoi_history.xlsx
+++ b/hanoi_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E528"/>
+  <dimension ref="A1:E532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12214,11 +12214,7 @@
           <t>ฮานอย</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
+      <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr">
         <is>
           <t>87</t>
@@ -12241,11 +12237,7 @@
           <t>ฮานอย VIP</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>073</t>
-        </is>
-      </c>
+      <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
           <t>73</t>
@@ -12268,11 +12260,7 @@
           <t>ฮานอยพิเศษ</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
+      <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr">
         <is>
           <t>92</t>
@@ -12295,11 +12283,7 @@
           <t>ฮานอยเฉพาะกิจ</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
+      <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
           <t>75</t>
@@ -12632,6 +12616,114 @@
       <c r="E528" t="inlineStr">
         <is>
           <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>12 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>ฮานอย</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>12 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>ฮานอย VIP</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>12 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>ฮานอยพิเศษ</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>12 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>ฮานอยเฉพาะกิจ</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
